--- a/dist/Modelo-Financiero-Clima-Baires-Argentina_v1.2.xlsx
+++ b/dist/Modelo-Financiero-Clima-Baires-Argentina_v1.2.xlsx
@@ -835,7 +835,7 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>La curva de obras/mes es el supuesto más frágil del modelo: es un pronóstico, no un dato verificable.</t>
+          <t>La curva de instalaciones/mes es el supuesto más frágil del modelo: es un pronóstico, no un dato verificable.</t>
         </is>
       </c>
     </row>
@@ -866,14 +866,14 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>Supuestos — lo único editable. Mix de producto, costos, estructura, marketing y obras mes a mes.</t>
+          <t>Supuestos — lo único editable. Mix de producto, costos, estructura, marketing y instalaciones mes a mes.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>Unit economics — qué deja cada obra, por categoría y en promedio ponderado.</t>
+          <t>Unit economics — qué deja cada instalación, por categoría y en promedio ponderado.</t>
         </is>
       </c>
     </row>
@@ -894,7 +894,7 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>Break-even — obras/mes necesarias según qué estructura haya que cubrir.</t>
+          <t>Break-even — instalaciones/mes necesarias según qué estructura haya que cubrir.</t>
         </is>
       </c>
     </row>
@@ -1011,7 +1011,7 @@
       </c>
       <c r="G4" s="9" t="inlineStr">
         <is>
-          <t>Elegir de la lista: cambia obras y ticket de todo el modelo.</t>
+          <t>Elegir de la lista: cambia instalaciones y ticket de todo el modelo.</t>
         </is>
       </c>
     </row>
@@ -1051,7 +1051,7 @@
       </c>
       <c r="B8" s="13" t="inlineStr">
         <is>
-          <t>Obras ×</t>
+          <t>Instalaciones ×</t>
         </is>
       </c>
       <c r="C8" s="13" t="inlineStr">
@@ -1133,7 +1133,7 @@
     <row r="14">
       <c r="A14" s="11" t="inlineStr">
         <is>
-          <t>Mix de producto y economía de la obra</t>
+          <t>Mix de producto y economía de la instalación</t>
         </is>
       </c>
       <c r="B14" s="12" t="n"/>
@@ -1357,7 +1357,7 @@
       </c>
       <c r="G25" s="9" t="inlineStr">
         <is>
-          <t>Pauta dividida por obras cerradas.</t>
+          <t>Pauta dividida por instalaciones cerradas.</t>
         </is>
       </c>
     </row>
@@ -1766,7 +1766,7 @@
     <row r="50">
       <c r="A50" s="7" t="inlineStr">
         <is>
-          <t>Obras del mes (antes del escenario)</t>
+          <t>Instalaciones del mes (antes del escenario)</t>
         </is>
       </c>
       <c r="B50" s="17" t="n">
@@ -1955,14 +1955,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Unit economics — qué deja cada obra</t>
+          <t>Unit economics — qué deja cada instalación</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>Todo se calcula desde «Supuestos». La obra tipo es el promedio ponderado por el mix.</t>
+          <t>Todo se calcula desde «Supuestos». La instalación tipo es el promedio ponderado por el mix.</t>
         </is>
       </c>
     </row>
@@ -1989,7 +1989,7 @@
       </c>
       <c r="E4" s="13" t="inlineStr">
         <is>
-          <t>Instalación</t>
+          <t>Montaje</t>
         </is>
       </c>
       <c r="F4" s="13" t="inlineStr">
@@ -2189,7 +2189,7 @@
     <row r="9">
       <c r="A9" s="11" t="inlineStr">
         <is>
-          <t>OBRA TIPO (promedio ponderado)</t>
+          <t>INSTALACIÓN TIPO (promedio ponderado)</t>
         </is>
       </c>
       <c r="B9" s="15">
@@ -2243,7 +2243,7 @@
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>CONTRIBUCIÓN NETA POR OBRA TIPO</t>
+          <t>CONTRIBUCIÓN NETA POR INSTALACIÓN TIPO</t>
         </is>
       </c>
       <c r="B12" s="18">
@@ -2274,7 +2274,7 @@
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>Costo del equipo de la obra tipo</t>
+          <t>Costo del equipo de la instalación tipo</t>
         </is>
       </c>
       <c r="B14" s="21">
@@ -2494,7 +2494,7 @@
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Obras</t>
+          <t>Instalaciones</t>
         </is>
       </c>
       <c r="B5" s="23">
@@ -2827,7 +2827,7 @@
     <row r="8">
       <c r="A8" s="9" t="inlineStr">
         <is>
-          <t>Instalación subcontratada</t>
+          <t>Montaje subcontratado</t>
         </is>
       </c>
       <c r="B8" s="21">
@@ -5422,14 +5422,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Punto de equilibrio — cuántas obras hay que hacer</t>
+          <t>Punto de equilibrio — cuántas instalaciones hay que hacer</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>Obras/mes necesarias para cubrir cada nivel de estructura, con la contribución de la obra tipo.</t>
+          <t>Instalaciones/mes necesarias para cubrir cada nivel de estructura, con la contribución de la instalación tipo.</t>
         </is>
       </c>
     </row>
@@ -5446,12 +5446,12 @@
       </c>
       <c r="C4" s="13" t="inlineStr">
         <is>
-          <t>Contribución por obra</t>
+          <t>Contribución por instalación</t>
         </is>
       </c>
       <c r="D4" s="13" t="inlineStr">
         <is>
-          <t>Obras/mes</t>
+          <t>Instalaciones/mes</t>
         </is>
       </c>
       <c r="E4" s="13" t="inlineStr">
@@ -5570,7 +5570,7 @@
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>Obras mínimas del mes valle proyectado</t>
+          <t>Instalaciones mínimas del mes valle proyectado</t>
         </is>
       </c>
       <c r="B11" s="23">
@@ -5641,7 +5641,7 @@
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Obras año 1</t>
+          <t>Instalaciones año 1</t>
         </is>
       </c>
       <c r="B5" s="25">
@@ -5850,7 +5850,7 @@
     <row r="5">
       <c r="A5" s="26" t="inlineStr">
         <is>
-          <t>Obras del año 1</t>
+          <t>Instalaciones del año 1</t>
         </is>
       </c>
       <c r="B5" s="23">
@@ -5978,7 +5978,7 @@
     <row r="14">
       <c r="A14" s="26" t="inlineStr">
         <is>
-          <t>Contribución por obra tipo</t>
+          <t>Contribución por instalación tipo</t>
         </is>
       </c>
       <c r="B14" s="18">
@@ -6003,7 +6003,7 @@
       </c>
       <c r="D15" s="9" t="inlineStr">
         <is>
-          <t>Obras/mes con la pauta al máximo.</t>
+          <t>Instalaciones/mes con la pauta al máximo.</t>
         </is>
       </c>
     </row>
@@ -6449,7 +6449,7 @@
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Obras año 1</t>
+          <t>Instalaciones año 1</t>
         </is>
       </c>
       <c r="B5" s="25">
@@ -6625,7 +6625,7 @@
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>Contribución por obra tipo</t>
+          <t>Contribución por instalación tipo</t>
         </is>
       </c>
       <c r="B13" s="21">
@@ -6647,7 +6647,7 @@
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>Break-even en temporada (obras/mes)</t>
+          <t>Break-even en temporada (instalaciones/mes)</t>
         </is>
       </c>
       <c r="B14" s="25">
